--- a/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.79632494102952</v>
+        <v>45.13824041665917</v>
       </c>
       <c r="M2" t="n">
-        <v>101.1984213076901</v>
+        <v>100.2609829451114</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.034558706639</v>
+        <v>88.09420969714901</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90019009611838</v>
+        <v>45.95100672082867</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228770821045089</v>
+        <v>2.228885194325119</v>
       </c>
       <c r="E3" t="n">
-        <v>5.690591414574829</v>
+        <v>5.722786878674169</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429236070150297</v>
+        <v>0.7429617314417063</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96313264346981</v>
+        <v>33.98016558905444</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17448592269136</v>
+        <v>34.17623964631849</v>
       </c>
       <c r="I3" t="n">
-        <v>6.591381753998951</v>
+        <v>6.599659835824447</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643272543843936</v>
+        <v>4.643510821510664</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96544129336099</v>
+        <v>11.90579030285095</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89777607469738</v>
+        <v>48.9063254609552</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634074641768</v>
+        <v>106.7631224846348</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19218890944758</v>
+        <v>87.30619299615029</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69851837696874</v>
+        <v>42.80340211413897</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188539927260943</v>
+        <v>2.191600077519455</v>
       </c>
       <c r="E4" t="n">
-        <v>6.505268322509056</v>
+        <v>6.545603436237163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444869471301825</v>
+        <v>0.7445250710321469</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35007401534421</v>
+        <v>33.41174042014515</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24639956798838</v>
+        <v>34.24815326747876</v>
       </c>
       <c r="I4" t="n">
-        <v>5.504376709651153</v>
+        <v>5.511289029786694</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65304341956364</v>
+        <v>4.653281693950918</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80781109055243</v>
+        <v>12.69380700384971</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31057659486775</v>
+        <v>44.31946699768286</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81690606238892</v>
+        <v>99.81667611567154</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.1983784972866</v>
+        <v>86.38834464775992</v>
       </c>
       <c r="C5" t="n">
-        <v>42.55905556531273</v>
+        <v>42.74107746623615</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140605433822477</v>
+        <v>2.14768109083314</v>
       </c>
       <c r="E5" t="n">
-        <v>7.128641935176057</v>
+        <v>7.181247277607929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745809870469089</v>
+        <v>0.7458468084049579</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61962405455157</v>
+        <v>32.74217949170249</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30725404157808</v>
+        <v>34.30895318662806</v>
       </c>
       <c r="I5" t="n">
-        <v>4.595131471257513</v>
+        <v>4.600894240052368</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661311690431805</v>
+        <v>4.661542552530986</v>
       </c>
       <c r="K5" t="n">
-        <v>13.80162150271341</v>
+        <v>13.61165535224007</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48642357892798</v>
+        <v>43.49417581958525</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84710064695413</v>
+        <v>99.84690863806148</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.052350988024</v>
+        <v>85.2402891317069</v>
       </c>
       <c r="C6" t="n">
-        <v>42.12686648909791</v>
+        <v>42.30791224139168</v>
       </c>
       <c r="D6" t="n">
-        <v>2.085170452191298</v>
+        <v>2.092211090481486</v>
       </c>
       <c r="E6" t="n">
-        <v>7.583204361733821</v>
+        <v>7.635743662726843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469308288875749</v>
+        <v>0.7469667518877608</v>
       </c>
       <c r="G6" t="n">
-        <v>31.77487787587305</v>
+        <v>31.89651915801945</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35881812882844</v>
+        <v>34.360470586837</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835031659962468</v>
+        <v>3.839835682455875</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668317680547343</v>
+        <v>4.668542199298504</v>
       </c>
       <c r="K6" t="n">
-        <v>14.94764901197602</v>
+        <v>14.75971086829307</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79784195805782</v>
+        <v>42.80457427253602</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87235745913173</v>
+        <v>99.87219738222078</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.65311637190752</v>
+        <v>84.0030204278118</v>
       </c>
       <c r="C7" t="n">
-        <v>41.32359218867517</v>
+        <v>41.66748247067263</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017338536943897</v>
+        <v>2.032601938508471</v>
       </c>
       <c r="E7" t="n">
-        <v>7.869840371149917</v>
+        <v>7.95218235361049</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478832261118663</v>
+        <v>0.7479164122268698</v>
       </c>
       <c r="G7" t="n">
-        <v>30.74122097707722</v>
+        <v>30.98775595216962</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40262840114585</v>
+        <v>34.404154962436</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199934696279598</v>
+        <v>3.203931232442413</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674270163199164</v>
+        <v>4.674477576417935</v>
       </c>
       <c r="K7" t="n">
-        <v>16.34688362809249</v>
+        <v>15.99697957218819</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22299552601118</v>
+        <v>42.22887585484873</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89347134277884</v>
+        <v>99.89333789770956</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.57798862057291</v>
+        <v>88.84003309295987</v>
       </c>
       <c r="C8" t="n">
-        <v>43.67725599357097</v>
+        <v>43.90692719894295</v>
       </c>
       <c r="D8" t="n">
-        <v>2.021626216741892</v>
+        <v>2.036931998954954</v>
       </c>
       <c r="E8" t="n">
-        <v>9.737584154552724</v>
+        <v>9.745302340321917</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494727876758455</v>
+        <v>0.7495097017010672</v>
       </c>
       <c r="G8" t="n">
-        <v>31.26140509092534</v>
+        <v>31.46871826938493</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47574823308889</v>
+        <v>34.47744627824908</v>
       </c>
       <c r="I8" t="n">
-        <v>5.647947214614195</v>
+        <v>5.677688868716252</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684204922974034</v>
+        <v>4.684435635631669</v>
       </c>
       <c r="K8" t="n">
-        <v>11.42201137942709</v>
+        <v>11.15996690704012</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71286701207752</v>
+        <v>44.74425191481811</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81213438507558</v>
+        <v>99.81114602080117</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.7887514509093</v>
+        <v>87.06732861662584</v>
       </c>
       <c r="C9" t="n">
-        <v>42.76528819337307</v>
+        <v>43.01632573246165</v>
       </c>
       <c r="D9" t="n">
-        <v>1.941055155062996</v>
+        <v>1.956990206233743</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13535454065052</v>
+        <v>10.15283538557729</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508300579517109</v>
+        <v>0.7508698257565569</v>
       </c>
       <c r="G9" t="n">
-        <v>30.01549495338804</v>
+        <v>30.23369139839266</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5381826657787</v>
+        <v>34.54001198480161</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715146215879137</v>
+        <v>4.739993404885507</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692687862198193</v>
+        <v>4.692936410978479</v>
       </c>
       <c r="K9" t="n">
-        <v>13.21124854909069</v>
+        <v>12.93267138337416</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86657583490808</v>
+        <v>43.89328930447763</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84311257737184</v>
+        <v>99.84228642031343</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.80435347637078</v>
+        <v>84.99427804563615</v>
       </c>
       <c r="C10" t="n">
-        <v>41.51321815138684</v>
+        <v>41.67966866231576</v>
       </c>
       <c r="D10" t="n">
-        <v>1.852406209796939</v>
+        <v>1.864067701587944</v>
       </c>
       <c r="E10" t="n">
-        <v>10.32836232176373</v>
+        <v>10.33010868336095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519914729560159</v>
+        <v>0.7520348192405009</v>
       </c>
       <c r="G10" t="n">
-        <v>28.64467251059653</v>
+        <v>28.79812451590247</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59160775597673</v>
+        <v>34.59360168506303</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935366499305736</v>
+        <v>3.956123020228128</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699946705975099</v>
+        <v>4.700217620253129</v>
       </c>
       <c r="K10" t="n">
-        <v>15.19564652362923</v>
+        <v>15.00572195436386</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1601590412095</v>
+        <v>43.18294289985134</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86902371622557</v>
+        <v>99.86833351653095</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.71107843821949</v>
+        <v>82.869040940416</v>
       </c>
       <c r="C11" t="n">
-        <v>40.03073615742107</v>
+        <v>40.16856014545898</v>
       </c>
       <c r="D11" t="n">
-        <v>1.759752115167452</v>
+        <v>1.769772396958178</v>
       </c>
       <c r="E11" t="n">
-        <v>10.35905786366582</v>
+        <v>10.35774329273566</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529866635997966</v>
+        <v>0.753033413860319</v>
       </c>
       <c r="G11" t="n">
-        <v>27.21191646422243</v>
+        <v>27.34134914144602</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63738652559064</v>
+        <v>34.63953703757466</v>
       </c>
       <c r="I11" t="n">
-        <v>3.283812158474612</v>
+        <v>3.301146821214171</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706166647498729</v>
+        <v>4.706458836626993</v>
       </c>
       <c r="K11" t="n">
-        <v>17.2889215617805</v>
+        <v>17.13095905958399</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57102654470661</v>
+        <v>42.59058848883959</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89068426390818</v>
+        <v>99.89010769388257</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.52152367472955</v>
+        <v>80.65832806385217</v>
       </c>
       <c r="C12" t="n">
-        <v>38.35024336517592</v>
+        <v>38.46967798249386</v>
       </c>
       <c r="D12" t="n">
-        <v>1.663670775485164</v>
+        <v>1.672546153515538</v>
       </c>
       <c r="E12" t="n">
-        <v>10.2500622052112</v>
+        <v>10.24773290037039</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538406350771132</v>
+        <v>0.7538904939202901</v>
       </c>
       <c r="G12" t="n">
-        <v>25.72616323416809</v>
+        <v>25.83929346906384</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67666921354721</v>
+        <v>34.67896272033333</v>
       </c>
       <c r="I12" t="n">
-        <v>2.739613642008817</v>
+        <v>2.754086739646964</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711503969231958</v>
+        <v>4.711815587001812</v>
       </c>
       <c r="K12" t="n">
-        <v>19.47847632527045</v>
+        <v>19.34167193614783</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08006330515155</v>
+        <v>42.0969515585468</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90878299559792</v>
+        <v>99.90830147718849</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.29953671319115</v>
+        <v>78.33792874619304</v>
       </c>
       <c r="C13" t="n">
-        <v>36.55225178312661</v>
+        <v>36.57557574638414</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56698266944878</v>
+        <v>1.571299415545999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.03522801114009</v>
+        <v>10.0102775188008</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545740157706964</v>
+        <v>0.7546274398454331</v>
       </c>
       <c r="G13" t="n">
-        <v>24.23102727617232</v>
+        <v>24.27512486918308</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71040472545203</v>
+        <v>34.71286223288991</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285232416640366</v>
+        <v>2.297315770893851</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716087598566853</v>
+        <v>4.716421499033956</v>
       </c>
       <c r="K13" t="n">
-        <v>21.70046328680885</v>
+        <v>21.66207125380695</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67118455111984</v>
+        <v>41.68585059037429</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92389962105531</v>
+        <v>99.92349759056538</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.6076686189664</v>
+        <v>84.6083951122675</v>
       </c>
       <c r="C14" t="n">
-        <v>40.47786699666781</v>
+        <v>40.30187281695655</v>
       </c>
       <c r="D14" t="n">
-        <v>1.568777177065371</v>
+        <v>1.573277621415342</v>
       </c>
       <c r="E14" t="n">
-        <v>12.23620693352138</v>
+        <v>12.13677182267871</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554381534826079</v>
+        <v>0.7555774869312403</v>
       </c>
       <c r="G14" t="n">
-        <v>25.96379996169262</v>
+        <v>25.8869844024503</v>
       </c>
       <c r="H14" t="n">
-        <v>36.45517838776455</v>
+        <v>36.33786247830356</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906779546173561</v>
+        <v>3.195562007168125</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7214884592663</v>
+        <v>4.722359293320251</v>
       </c>
       <c r="K14" t="n">
-        <v>15.39233138103362</v>
+        <v>15.39160488773247</v>
       </c>
       <c r="L14" t="n">
-        <v>44.0330198052385</v>
+        <v>44.20013749613214</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90321818293992</v>
+        <v>99.89361520082116</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.94706040625576</v>
+        <v>83.87103386403888</v>
       </c>
       <c r="C15" t="n">
-        <v>40.26733339446434</v>
+        <v>40.05907814179805</v>
       </c>
       <c r="D15" t="n">
-        <v>1.544203147388755</v>
+        <v>1.545616446365223</v>
       </c>
       <c r="E15" t="n">
-        <v>12.44864156707718</v>
+        <v>12.36768286569502</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561654657973457</v>
+        <v>0.7563780059302889</v>
       </c>
       <c r="G15" t="n">
-        <v>25.55709134806407</v>
+        <v>25.43184260336229</v>
       </c>
       <c r="H15" t="n">
-        <v>36.49027629757379</v>
+        <v>36.37636170545343</v>
       </c>
       <c r="I15" t="n">
-        <v>2.424648419121195</v>
+        <v>2.6657897001683</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726034161233411</v>
+        <v>4.727362537064304</v>
       </c>
       <c r="K15" t="n">
-        <v>16.05293959374425</v>
+        <v>16.12896613596113</v>
       </c>
       <c r="L15" t="n">
-        <v>43.59898313550882</v>
+        <v>43.72319011093058</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9192561237174</v>
+        <v>99.91123438868976</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.60465947130808</v>
+        <v>81.47133813307133</v>
       </c>
       <c r="C16" t="n">
-        <v>38.30045731825762</v>
+        <v>38.07207275985313</v>
       </c>
       <c r="D16" t="n">
-        <v>1.45394552564674</v>
+        <v>1.452668241290364</v>
       </c>
       <c r="E16" t="n">
-        <v>12.05806184225412</v>
+        <v>11.99451716784866</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567900726468463</v>
+        <v>0.7570661071683312</v>
       </c>
       <c r="G16" t="n">
-        <v>24.06329677341867</v>
+        <v>23.90245662452657</v>
       </c>
       <c r="H16" t="n">
-        <v>36.52041794982658</v>
+        <v>36.40945444391059</v>
       </c>
       <c r="I16" t="n">
-        <v>2.022209353472336</v>
+        <v>2.223512378524762</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729937954042789</v>
+        <v>4.731663169802069</v>
       </c>
       <c r="K16" t="n">
-        <v>18.39534052869193</v>
+        <v>18.52866186692865</v>
       </c>
       <c r="L16" t="n">
-        <v>43.23685080807486</v>
+        <v>43.32521565932465</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93264865502441</v>
+        <v>99.92595028610643</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.11974161588695</v>
+        <v>82.93754887693284</v>
       </c>
       <c r="C17" t="n">
-        <v>39.42110597249114</v>
+        <v>39.14006047379054</v>
       </c>
       <c r="D17" t="n">
-        <v>1.455114927050422</v>
+        <v>1.45398442191295</v>
       </c>
       <c r="E17" t="n">
-        <v>12.77983592870536</v>
+        <v>12.71039158813229</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573987552677799</v>
+        <v>0.7577520419963594</v>
       </c>
       <c r="G17" t="n">
-        <v>24.46046256768077</v>
+        <v>24.25339501926307</v>
       </c>
       <c r="H17" t="n">
-        <v>36.92760294682535</v>
+        <v>36.77172472276813</v>
       </c>
       <c r="I17" t="n">
-        <v>2.005584269933657</v>
+        <v>2.254350820382797</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733742220423625</v>
+        <v>4.735950262477244</v>
       </c>
       <c r="K17" t="n">
-        <v>16.88025838411304</v>
+        <v>17.06245112306717</v>
       </c>
       <c r="L17" t="n">
-        <v>43.63183656057954</v>
+        <v>43.72241139882821</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93320091718371</v>
+        <v>99.92492299568592</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.9407820387423</v>
+        <v>80.66020836234561</v>
       </c>
       <c r="C18" t="n">
-        <v>37.55240597238378</v>
+        <v>37.21128683732615</v>
       </c>
       <c r="D18" t="n">
-        <v>1.374122415315216</v>
+        <v>1.368857401191157</v>
       </c>
       <c r="E18" t="n">
-        <v>12.34724833211325</v>
+        <v>12.27957864162077</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579204237852913</v>
+        <v>0.7583407827151081</v>
       </c>
       <c r="G18" t="n">
-        <v>23.09897952277981</v>
+        <v>22.83342157988998</v>
       </c>
       <c r="H18" t="n">
-        <v>36.95303732699898</v>
+        <v>36.80029477001719</v>
       </c>
       <c r="I18" t="n">
-        <v>1.672471369091664</v>
+        <v>1.880085294941981</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737002648658071</v>
+        <v>4.739629891969424</v>
       </c>
       <c r="K18" t="n">
-        <v>19.05921796125771</v>
+        <v>19.3397916376544</v>
       </c>
       <c r="L18" t="n">
-        <v>43.33266539219368</v>
+        <v>43.3863006688977</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94428932583517</v>
+        <v>99.93737914387825</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.04210000775181</v>
+        <v>79.69537617104297</v>
       </c>
       <c r="C19" t="n">
-        <v>36.91187635315471</v>
+        <v>36.53648917174521</v>
       </c>
       <c r="D19" t="n">
-        <v>1.341362465860564</v>
+        <v>1.33352922596518</v>
       </c>
       <c r="E19" t="n">
-        <v>12.28530469622622</v>
+        <v>12.22395515032261</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583605867219825</v>
+        <v>0.7588380513041767</v>
       </c>
       <c r="G19" t="n">
-        <v>22.54828520822216</v>
+        <v>22.24412490232444</v>
       </c>
       <c r="H19" t="n">
-        <v>36.9744978351461</v>
+        <v>36.8244259140552</v>
       </c>
       <c r="I19" t="n">
-        <v>1.394535548562389</v>
+        <v>1.567765106420261</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739753667012391</v>
+        <v>4.742737820651103</v>
       </c>
       <c r="K19" t="n">
-        <v>19.95789999224819</v>
+        <v>20.30462382895704</v>
       </c>
       <c r="L19" t="n">
-        <v>43.08376611656677</v>
+        <v>43.10666240777159</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95354246196968</v>
+        <v>99.94777540847383</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.52364225700154</v>
+        <v>77.17897027299458</v>
       </c>
       <c r="C20" t="n">
-        <v>34.60854069913655</v>
+        <v>34.26178658553751</v>
       </c>
       <c r="D20" t="n">
-        <v>1.248602287367535</v>
+        <v>1.240498744069478</v>
       </c>
       <c r="E20" t="n">
-        <v>11.6295127344862</v>
+        <v>11.58904819884057</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587397146145737</v>
+        <v>0.759266475251127</v>
       </c>
       <c r="G20" t="n">
-        <v>20.98898784165649</v>
+        <v>20.69231664891803</v>
       </c>
       <c r="H20" t="n">
-        <v>36.99298252922078</v>
+        <v>36.84521620767209</v>
       </c>
       <c r="I20" t="n">
-        <v>1.16269393331487</v>
+        <v>1.307208527923737</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742123216341086</v>
+        <v>4.745415470319542</v>
       </c>
       <c r="K20" t="n">
-        <v>22.47635774299845</v>
+        <v>22.82102972700542</v>
       </c>
       <c r="L20" t="n">
-        <v>42.87636445929381</v>
+        <v>42.87363465672318</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96126290142882</v>
+        <v>99.95645096926611</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.93905095092035</v>
+        <v>82.63997133029856</v>
       </c>
       <c r="C21" t="n">
-        <v>37.93906822629242</v>
+        <v>37.50366913780411</v>
       </c>
       <c r="D21" t="n">
-        <v>1.24945239354934</v>
+        <v>1.241518425839375</v>
       </c>
       <c r="E21" t="n">
-        <v>13.43634322129831</v>
+        <v>13.38099208393352</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592562997019955</v>
+        <v>0.7598905872762369</v>
       </c>
       <c r="G21" t="n">
-        <v>22.51984698397316</v>
+        <v>22.15209580894652</v>
       </c>
       <c r="H21" t="n">
-        <v>38.53473793126332</v>
+        <v>38.31827294439283</v>
       </c>
       <c r="I21" t="n">
-        <v>1.694062247996762</v>
+        <v>2.037885309433609</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745351873137472</v>
+        <v>4.749316170476479</v>
       </c>
       <c r="K21" t="n">
-        <v>17.06094904907967</v>
+        <v>17.36002866970142</v>
       </c>
       <c r="L21" t="n">
-        <v>44.94355240340045</v>
+        <v>45.06842847392814</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94356967877253</v>
+        <v>99.93212628143368</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.13824041665917</v>
+        <v>45.43023887945582</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2609829451114</v>
+        <v>99.69063134374005</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09420969714901</v>
+        <v>88.10801306987074</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95100672082867</v>
+        <v>45.94343219640579</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228885194325119</v>
+        <v>2.228926292709306</v>
       </c>
       <c r="E3" t="n">
-        <v>5.722786878674169</v>
+        <v>5.719270085981313</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429617314417063</v>
+        <v>0.7429754309031021</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98016558905444</v>
+        <v>33.97737985702133</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17623964631849</v>
+        <v>34.1768698215427</v>
       </c>
       <c r="I3" t="n">
-        <v>6.599659835824447</v>
+        <v>6.618995138568604</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643510821510664</v>
+        <v>4.643596443144388</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90579030285095</v>
+        <v>11.89198693012925</v>
       </c>
       <c r="L3" t="n">
-        <v>48.9063254609552</v>
+        <v>48.92701374851448</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631224846348</v>
+        <v>106.7624328750495</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30619299615029</v>
+        <v>87.35424425727621</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80340211413897</v>
+        <v>42.83408773437723</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191600077519455</v>
+        <v>2.193469777220294</v>
       </c>
       <c r="E4" t="n">
-        <v>6.545603436237163</v>
+        <v>6.549535020312259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445250710321469</v>
+        <v>0.7445425249410189</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41174042014515</v>
+        <v>33.43688666120904</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24815326747876</v>
+        <v>34.24895614728687</v>
       </c>
       <c r="I4" t="n">
-        <v>5.511289029786694</v>
+        <v>5.527463345425345</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653281693950918</v>
+        <v>4.653390780881368</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69380700384971</v>
+        <v>12.64575574272383</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31946699768286</v>
+        <v>44.33629554682759</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81667611567154</v>
+        <v>99.81613902392863</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.38834464775992</v>
+        <v>86.27355615536925</v>
       </c>
       <c r="C5" t="n">
-        <v>42.74107746623615</v>
+        <v>42.61144912419589</v>
       </c>
       <c r="D5" t="n">
-        <v>2.14768109083314</v>
+        <v>2.141081511572203</v>
       </c>
       <c r="E5" t="n">
-        <v>7.181247277607929</v>
+        <v>7.16217957366651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458468084049579</v>
+        <v>0.7458699462313022</v>
       </c>
       <c r="G5" t="n">
-        <v>32.74217949170249</v>
+        <v>32.6382886959923</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30895318662806</v>
+        <v>34.3100175266399</v>
       </c>
       <c r="I5" t="n">
-        <v>4.600894240052368</v>
+        <v>4.614431737321398</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661542552530986</v>
+        <v>4.661687163945639</v>
       </c>
       <c r="K5" t="n">
-        <v>13.61165535224007</v>
+        <v>13.72644384463075</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49417581958525</v>
+        <v>43.50856638268935</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84690863806148</v>
+        <v>99.84645935151599</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.2402891317069</v>
+        <v>85.13813397905101</v>
       </c>
       <c r="C6" t="n">
-        <v>42.30791224139168</v>
+        <v>42.19289084799429</v>
       </c>
       <c r="D6" t="n">
-        <v>2.092211090481486</v>
+        <v>2.086260089220878</v>
       </c>
       <c r="E6" t="n">
-        <v>7.635743662726843</v>
+        <v>7.620654850277512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469667518877608</v>
+        <v>0.7469945746282093</v>
       </c>
       <c r="G6" t="n">
-        <v>31.89651915801945</v>
+        <v>31.80260009667616</v>
       </c>
       <c r="H6" t="n">
-        <v>34.360470586837</v>
+        <v>34.36175043289763</v>
       </c>
       <c r="I6" t="n">
-        <v>3.839835682455875</v>
+        <v>3.851157843924318</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668542199298504</v>
+        <v>4.668716091426308</v>
       </c>
       <c r="K6" t="n">
-        <v>14.75971086829307</v>
+        <v>14.86186602094897</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80457427253602</v>
+        <v>42.81706447168671</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87219738222078</v>
+        <v>99.87182134062996</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84.0030204278118</v>
+        <v>83.8022689479503</v>
       </c>
       <c r="C7" t="n">
-        <v>41.66748247067263</v>
+        <v>41.45552761358041</v>
       </c>
       <c r="D7" t="n">
-        <v>2.032601938508471</v>
+        <v>2.021700547983538</v>
       </c>
       <c r="E7" t="n">
-        <v>7.95218235361049</v>
+        <v>7.920399576197323</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479164122268698</v>
+        <v>0.7479493588536806</v>
       </c>
       <c r="G7" t="n">
-        <v>30.98775595216962</v>
+        <v>30.81846524071831</v>
       </c>
       <c r="H7" t="n">
-        <v>34.404154962436</v>
+        <v>34.40567050726931</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203931232442413</v>
+        <v>3.213400224092627</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674477576417935</v>
+        <v>4.674683492835505</v>
       </c>
       <c r="K7" t="n">
-        <v>15.99697957218819</v>
+        <v>16.1977310520497</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22887585484873</v>
+        <v>42.23976472759421</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89333789770956</v>
+        <v>99.89302339322433</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.84003309295987</v>
+        <v>88.7119629952316</v>
       </c>
       <c r="C8" t="n">
-        <v>43.90692719894295</v>
+        <v>43.79690432892497</v>
       </c>
       <c r="D8" t="n">
-        <v>2.036931998954954</v>
+        <v>2.025999021213978</v>
       </c>
       <c r="E8" t="n">
-        <v>9.745302340321917</v>
+        <v>9.780437169986667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495097017010672</v>
+        <v>0.749539624187468</v>
       </c>
       <c r="G8" t="n">
-        <v>31.46871826938493</v>
+        <v>31.33404805145348</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47744627824908</v>
+        <v>34.47882271262353</v>
       </c>
       <c r="I8" t="n">
-        <v>5.677688868716252</v>
+        <v>5.658493764594795</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684435635631669</v>
+        <v>4.684622651171676</v>
       </c>
       <c r="K8" t="n">
-        <v>11.15996690704012</v>
+        <v>11.2880370047684</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74425191481811</v>
+        <v>44.72684238675173</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81114602080117</v>
+        <v>99.81178372044509</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.06732861662584</v>
+        <v>86.94451915249213</v>
       </c>
       <c r="C9" t="n">
-        <v>43.01632573246165</v>
+        <v>42.90848193585143</v>
       </c>
       <c r="D9" t="n">
-        <v>1.956990206233743</v>
+        <v>1.946513819212037</v>
       </c>
       <c r="E9" t="n">
-        <v>10.15283538557729</v>
+        <v>10.18405048260859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508698257565569</v>
+        <v>0.7508971139594287</v>
       </c>
       <c r="G9" t="n">
-        <v>30.23369139839266</v>
+        <v>30.10473198919006</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54001198480161</v>
+        <v>34.54126724213372</v>
       </c>
       <c r="I9" t="n">
-        <v>4.739993404885507</v>
+        <v>4.723951543141887</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692936410978479</v>
+        <v>4.69310696224643</v>
       </c>
       <c r="K9" t="n">
-        <v>12.93267138337416</v>
+        <v>13.05548084750785</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89328930447763</v>
+        <v>43.87885683429087</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84228642031343</v>
+        <v>99.84281961765015</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.99427804563615</v>
+        <v>84.92462276458697</v>
       </c>
       <c r="C10" t="n">
-        <v>41.67966866231576</v>
+        <v>41.62240139805686</v>
       </c>
       <c r="D10" t="n">
-        <v>1.864067701587944</v>
+        <v>1.856290340796495</v>
       </c>
       <c r="E10" t="n">
-        <v>10.33010868336095</v>
+        <v>10.3691260602233</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520348192405009</v>
+        <v>0.7520591545785595</v>
       </c>
       <c r="G10" t="n">
-        <v>28.79812451590247</v>
+        <v>28.70933802382284</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59360168506303</v>
+        <v>34.59472111061374</v>
       </c>
       <c r="I10" t="n">
-        <v>3.956123020228128</v>
+        <v>3.942718358436034</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700217620253129</v>
+        <v>4.700369716115998</v>
       </c>
       <c r="K10" t="n">
-        <v>15.00572195436386</v>
+        <v>15.07537723541303</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18294289985134</v>
+        <v>43.17100049033172</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86833351653095</v>
+        <v>99.86877912380162</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.869040940416</v>
+        <v>82.74562256035772</v>
       </c>
       <c r="C11" t="n">
-        <v>40.16856014545898</v>
+        <v>40.05541314719696</v>
       </c>
       <c r="D11" t="n">
-        <v>1.769772396958178</v>
+        <v>1.759807280911429</v>
       </c>
       <c r="E11" t="n">
-        <v>10.35774329273566</v>
+        <v>10.37850301920077</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753033413860319</v>
+        <v>0.7530558797594293</v>
       </c>
       <c r="G11" t="n">
-        <v>27.34134914144602</v>
+        <v>27.21713353461315</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63953703757466</v>
+        <v>34.64057046893375</v>
       </c>
       <c r="I11" t="n">
-        <v>3.301146821214171</v>
+        <v>3.289953128442761</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706458836626993</v>
+        <v>4.706599248496434</v>
       </c>
       <c r="K11" t="n">
-        <v>17.13095905958399</v>
+        <v>17.25437743964226</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59058848883959</v>
+        <v>42.58068945875977</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89010769388257</v>
+        <v>99.89048004559899</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.65832806385217</v>
+        <v>80.37187759913807</v>
       </c>
       <c r="C12" t="n">
-        <v>38.46967798249386</v>
+        <v>38.19169268777104</v>
       </c>
       <c r="D12" t="n">
-        <v>1.672546153515538</v>
+        <v>1.65554600324992</v>
       </c>
       <c r="E12" t="n">
-        <v>10.24773290037039</v>
+        <v>10.22107788070031</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538904939202901</v>
+        <v>0.7539131236507222</v>
       </c>
       <c r="G12" t="n">
-        <v>25.83929346906384</v>
+        <v>25.60463133202368</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67896272033333</v>
+        <v>34.68000368793322</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754086739646964</v>
+        <v>2.744748548763202</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711815587001812</v>
+        <v>4.711957022817014</v>
       </c>
       <c r="K12" t="n">
-        <v>19.34167193614783</v>
+        <v>19.62812240086195</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0969515585468</v>
+        <v>42.08879732446582</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90830147718849</v>
+        <v>99.90861241309881</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.33792874619304</v>
+        <v>77.90328905114359</v>
       </c>
       <c r="C13" t="n">
-        <v>36.57557574638414</v>
+        <v>36.14779486784728</v>
       </c>
       <c r="D13" t="n">
-        <v>1.571299415545999</v>
+        <v>1.54802354764913</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0102775188008</v>
+        <v>9.938839862486923</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546274398454331</v>
+        <v>0.7546516922166188</v>
       </c>
       <c r="G13" t="n">
-        <v>24.27512486918308</v>
+        <v>23.94169183643269</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71286223288991</v>
+        <v>34.71397784196446</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297315770893851</v>
+        <v>2.289531194039891</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716421499033956</v>
+        <v>4.716573076353868</v>
       </c>
       <c r="K13" t="n">
-        <v>21.66207125380695</v>
+        <v>22.09671094885641</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68585059037429</v>
+        <v>41.6792511680529</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92349759056538</v>
+        <v>99.92375698475659</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.6083951122675</v>
+        <v>84.21911251257957</v>
       </c>
       <c r="C14" t="n">
-        <v>40.30187281695655</v>
+        <v>40.03875233219462</v>
       </c>
       <c r="D14" t="n">
-        <v>1.573277621415342</v>
+        <v>1.549845745757997</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13677182267871</v>
+        <v>12.12841935693482</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555774869312403</v>
+        <v>0.7555400022739811</v>
       </c>
       <c r="G14" t="n">
-        <v>25.8869844024503</v>
+        <v>25.65207734930634</v>
       </c>
       <c r="H14" t="n">
-        <v>36.33786247830356</v>
+        <v>36.43704354902331</v>
       </c>
       <c r="I14" t="n">
-        <v>3.195562007168125</v>
+        <v>2.974061495070749</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722359293320251</v>
+        <v>4.722125014212382</v>
       </c>
       <c r="K14" t="n">
-        <v>15.39160488773247</v>
+        <v>15.78088748742042</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20013749613214</v>
+        <v>44.08134135353015</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89361520082116</v>
+        <v>99.90098117314518</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.87103386403888</v>
+        <v>83.2830946163966</v>
       </c>
       <c r="C15" t="n">
-        <v>40.05907814179805</v>
+        <v>39.56292865462774</v>
       </c>
       <c r="D15" t="n">
-        <v>1.545616446365223</v>
+        <v>1.514463435680732</v>
       </c>
       <c r="E15" t="n">
-        <v>12.36768286569502</v>
+        <v>12.26500701590442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563780059302889</v>
+        <v>0.7562902057384239</v>
       </c>
       <c r="G15" t="n">
-        <v>25.43184260336229</v>
+        <v>25.06645148467859</v>
       </c>
       <c r="H15" t="n">
-        <v>36.37636170545343</v>
+        <v>36.47322323007562</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6657897001683</v>
+        <v>2.480845458453674</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727362537064304</v>
+        <v>4.726813785865149</v>
       </c>
       <c r="K15" t="n">
-        <v>16.12896613596113</v>
+        <v>16.71690538360341</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72319011093058</v>
+        <v>43.63755314246132</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91123438868976</v>
+        <v>99.91738718069246</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.47133813307133</v>
+        <v>80.60708599406878</v>
       </c>
       <c r="C16" t="n">
-        <v>38.07207275985313</v>
+        <v>37.27076538890406</v>
       </c>
       <c r="D16" t="n">
-        <v>1.452668241290364</v>
+        <v>1.411342019455864</v>
       </c>
       <c r="E16" t="n">
-        <v>11.99451716784866</v>
+        <v>11.77472641636053</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570661071683312</v>
+        <v>0.7569373243785807</v>
       </c>
       <c r="G16" t="n">
-        <v>23.90245662452657</v>
+        <v>23.35965030616738</v>
       </c>
       <c r="H16" t="n">
-        <v>36.40945444391059</v>
+        <v>36.5044314917187</v>
       </c>
       <c r="I16" t="n">
-        <v>2.223512378524762</v>
+        <v>2.069140158621599</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731663169802069</v>
+        <v>4.73085827736613</v>
       </c>
       <c r="K16" t="n">
-        <v>18.52866186692865</v>
+        <v>19.3929140059312</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32521565932465</v>
+        <v>43.26740823131883</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92595028610643</v>
+        <v>99.9310876261541</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.93754887693284</v>
+        <v>82.03520492700549</v>
       </c>
       <c r="C17" t="n">
-        <v>39.14006047379054</v>
+        <v>38.32386305502666</v>
       </c>
       <c r="D17" t="n">
-        <v>1.45398442191295</v>
+        <v>1.412529466037132</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71039158813229</v>
+        <v>12.46821912431312</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577520419963594</v>
+        <v>0.757574181090616</v>
       </c>
       <c r="G17" t="n">
-        <v>24.25339501926307</v>
+        <v>23.71778444519819</v>
       </c>
       <c r="H17" t="n">
-        <v>36.77172472276813</v>
+        <v>36.87362512254181</v>
       </c>
       <c r="I17" t="n">
-        <v>2.254350820382797</v>
+        <v>2.070633956008291</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735950262477244</v>
+        <v>4.73483863181635</v>
       </c>
       <c r="K17" t="n">
-        <v>17.06245112306717</v>
+        <v>17.96479507299449</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72241139882821</v>
+        <v>43.64237876290649</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92492299568592</v>
+        <v>99.93103689092764</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.66020836234561</v>
+        <v>79.46054212018711</v>
       </c>
       <c r="C18" t="n">
-        <v>37.21128683732615</v>
+        <v>36.06903245926627</v>
       </c>
       <c r="D18" t="n">
-        <v>1.368857401191157</v>
+        <v>1.31675576686768</v>
       </c>
       <c r="E18" t="n">
-        <v>12.27957864162077</v>
+        <v>11.910633153902</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583407827151081</v>
+        <v>0.7581229493079323</v>
       </c>
       <c r="G18" t="n">
-        <v>22.83342157988998</v>
+        <v>22.10964811456775</v>
       </c>
       <c r="H18" t="n">
-        <v>36.80029477001719</v>
+        <v>36.90033547517731</v>
       </c>
       <c r="I18" t="n">
-        <v>1.880085294941981</v>
+        <v>1.72677822718986</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739629891969424</v>
+        <v>4.738268433174577</v>
       </c>
       <c r="K18" t="n">
-        <v>19.3397916376544</v>
+        <v>20.53945787981288</v>
       </c>
       <c r="L18" t="n">
-        <v>43.3863006688977</v>
+        <v>43.33399205103174</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93737914387825</v>
+        <v>99.94248239011088</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.69537617104297</v>
+        <v>78.37964771528843</v>
       </c>
       <c r="C19" t="n">
-        <v>36.53648917174521</v>
+        <v>35.2540958890786</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33352922596518</v>
+        <v>1.277260296938065</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22395515032261</v>
+        <v>11.79335648263929</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588380513041767</v>
+        <v>0.7585871825724463</v>
       </c>
       <c r="G19" t="n">
-        <v>22.24412490232444</v>
+        <v>21.44647961799792</v>
       </c>
       <c r="H19" t="n">
-        <v>36.8244259140552</v>
+        <v>36.92293123384012</v>
       </c>
       <c r="I19" t="n">
-        <v>1.567765106420261</v>
+        <v>1.439863010222791</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742737820651103</v>
+        <v>4.741169891077789</v>
       </c>
       <c r="K19" t="n">
-        <v>20.30462382895704</v>
+        <v>21.62035228471157</v>
       </c>
       <c r="L19" t="n">
-        <v>43.10666240777159</v>
+        <v>43.07758576434344</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94777540847383</v>
+        <v>99.95203393813361</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.17897027299458</v>
+        <v>75.75292282771383</v>
       </c>
       <c r="C20" t="n">
-        <v>34.26178658553751</v>
+        <v>32.84893966621518</v>
       </c>
       <c r="D20" t="n">
-        <v>1.240498744069478</v>
+        <v>1.180685136658281</v>
       </c>
       <c r="E20" t="n">
-        <v>11.58904819884057</v>
+        <v>11.1017334796084</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759266475251127</v>
+        <v>0.7589879146801843</v>
       </c>
       <c r="G20" t="n">
-        <v>20.69231664891803</v>
+        <v>19.82488595262645</v>
       </c>
       <c r="H20" t="n">
-        <v>36.84521620767209</v>
+        <v>36.94243618250934</v>
       </c>
       <c r="I20" t="n">
-        <v>1.307208527923737</v>
+        <v>1.200519694880029</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745415470319542</v>
+        <v>4.743674466751151</v>
       </c>
       <c r="K20" t="n">
-        <v>22.82102972700542</v>
+        <v>24.24707717228617</v>
       </c>
       <c r="L20" t="n">
-        <v>42.87363465672318</v>
+        <v>42.86398696677024</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95645096926611</v>
+        <v>99.96000380527158</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.63997133029856</v>
+        <v>81.67211535606688</v>
       </c>
       <c r="C21" t="n">
-        <v>37.50366913780411</v>
+        <v>36.52004209593642</v>
       </c>
       <c r="D21" t="n">
-        <v>1.241518425839375</v>
+        <v>1.181517137144264</v>
       </c>
       <c r="E21" t="n">
-        <v>13.38099208393352</v>
+        <v>13.08159971588184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598905872762369</v>
+        <v>0.759522755252207</v>
       </c>
       <c r="G21" t="n">
-        <v>22.15209580894652</v>
+        <v>21.52313728504696</v>
       </c>
       <c r="H21" t="n">
-        <v>38.31827294439283</v>
+        <v>38.65274984185166</v>
       </c>
       <c r="I21" t="n">
-        <v>2.037885309433609</v>
+        <v>1.726571400563642</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749316170476479</v>
+        <v>4.747017220326293</v>
       </c>
       <c r="K21" t="n">
-        <v>17.36002866970142</v>
+        <v>18.32788464393314</v>
       </c>
       <c r="L21" t="n">
-        <v>45.06842847392814</v>
+        <v>45.09456140733436</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93212628143368</v>
+        <v>99.94248814720392</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_14_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43023887945582</v>
+        <v>43.61383027862425</v>
       </c>
       <c r="M2" t="n">
-        <v>99.69063134374005</v>
+        <v>94.89964499692815</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10801306987074</v>
+        <v>81.43154358484372</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94343219640579</v>
+        <v>43.18709914039929</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228926292709306</v>
+        <v>2.177728954399747</v>
       </c>
       <c r="E3" t="n">
-        <v>5.719270085981313</v>
+        <v>4.14655374780523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429754309031021</v>
+        <v>0.7376009496698267</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97737985702133</v>
+        <v>32.75667302242953</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1768698215427</v>
+        <v>33.92964368481202</v>
       </c>
       <c r="I3" t="n">
-        <v>6.618995138568604</v>
+        <v>3.073337290290945</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643596443144388</v>
+        <v>4.610005935436416</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89198693012925</v>
+        <v>18.56845641515627</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92701374851448</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7624328750495</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.35424425727621</v>
+        <v>88.46146791341776</v>
       </c>
       <c r="C4" t="n">
-        <v>42.83408773437723</v>
+        <v>42.7584841371826</v>
       </c>
       <c r="D4" t="n">
-        <v>2.193469777220294</v>
+        <v>2.183432423991208</v>
       </c>
       <c r="E4" t="n">
-        <v>6.549535020312259</v>
+        <v>6.508632455689465</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445425249410189</v>
+        <v>0.7395327256966712</v>
       </c>
       <c r="G4" t="n">
-        <v>33.43688666120904</v>
+        <v>33.43887095188686</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24895614728687</v>
+        <v>34.01850538204687</v>
       </c>
       <c r="I4" t="n">
-        <v>5.527463345425345</v>
+        <v>6.95041443850249</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653390780881368</v>
+        <v>4.622079535604194</v>
       </c>
       <c r="K4" t="n">
-        <v>12.64575574272383</v>
+        <v>11.53853208658223</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33629554682759</v>
+        <v>45.47190848088075</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81613902392863</v>
+        <v>99.76892470464558</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.27355615536925</v>
+        <v>87.278869347824</v>
       </c>
       <c r="C5" t="n">
-        <v>42.61144912419589</v>
+        <v>42.65320533035135</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141081511572203</v>
+        <v>2.126849088154422</v>
       </c>
       <c r="E5" t="n">
-        <v>7.16217957366651</v>
+        <v>7.307437649102641</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458699462313022</v>
+        <v>0.7411722514414762</v>
       </c>
       <c r="G5" t="n">
-        <v>32.6382886959923</v>
+        <v>32.57230744193636</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3100175266399</v>
+        <v>34.0939235663079</v>
       </c>
       <c r="I5" t="n">
-        <v>4.614431737321398</v>
+        <v>5.804852779371985</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661687163945639</v>
+        <v>4.632326571509226</v>
       </c>
       <c r="K5" t="n">
-        <v>13.72644384463075</v>
+        <v>12.72113065217599</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50856638268935</v>
+        <v>44.43259694973647</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84645935151599</v>
+        <v>99.80693293226381</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.13813397905101</v>
+        <v>85.81328315481589</v>
       </c>
       <c r="C6" t="n">
-        <v>42.19289084799429</v>
+        <v>42.08840979031734</v>
       </c>
       <c r="D6" t="n">
-        <v>2.086260089220878</v>
+        <v>2.056508778372197</v>
       </c>
       <c r="E6" t="n">
-        <v>7.620654850277512</v>
+        <v>7.873509432677159</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469945746282093</v>
+        <v>0.7425675596955977</v>
       </c>
       <c r="G6" t="n">
-        <v>31.80260009667616</v>
+        <v>31.49505837497231</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36175043289763</v>
+        <v>34.15810774599749</v>
       </c>
       <c r="I6" t="n">
-        <v>3.851157843924318</v>
+        <v>4.846484015003658</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668716091426308</v>
+        <v>4.641047248097485</v>
       </c>
       <c r="K6" t="n">
-        <v>14.86186602094897</v>
+        <v>14.18671684518411</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81706447168671</v>
+        <v>43.56362745396045</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87182134062996</v>
+        <v>99.83875408946189</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.8022689479503</v>
+        <v>84.20588158539785</v>
       </c>
       <c r="C7" t="n">
-        <v>41.45552761358041</v>
+        <v>41.23336535616084</v>
       </c>
       <c r="D7" t="n">
-        <v>2.021700547983538</v>
+        <v>1.97987618305034</v>
       </c>
       <c r="E7" t="n">
-        <v>7.920399576197323</v>
+        <v>8.254316032998968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479493588536806</v>
+        <v>0.7437566441881547</v>
       </c>
       <c r="G7" t="n">
-        <v>30.81846524071831</v>
+        <v>30.32144409796546</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40567050726931</v>
+        <v>34.21280563265511</v>
       </c>
       <c r="I7" t="n">
-        <v>3.213400224092627</v>
+        <v>4.045203968363833</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674683492835505</v>
+        <v>4.648479026175966</v>
       </c>
       <c r="K7" t="n">
-        <v>16.1977310520497</v>
+        <v>15.79411841460215</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23976472759421</v>
+        <v>42.83789167326469</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89302339322433</v>
+        <v>99.86537544402769</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.7119629952316</v>
+        <v>82.41735363247182</v>
       </c>
       <c r="C8" t="n">
-        <v>43.79690432892497</v>
+        <v>40.07269888977189</v>
       </c>
       <c r="D8" t="n">
-        <v>2.025999021213978</v>
+        <v>1.895146271057616</v>
       </c>
       <c r="E8" t="n">
-        <v>9.780437169986667</v>
+        <v>8.463668875055907</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749539624187468</v>
+        <v>0.7447720569850887</v>
       </c>
       <c r="G8" t="n">
-        <v>31.33404805145348</v>
+        <v>29.02382088702573</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47882271262353</v>
+        <v>34.25951462131408</v>
       </c>
       <c r="I8" t="n">
-        <v>5.658493764594795</v>
+        <v>3.375605564876599</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684622651171676</v>
+        <v>4.654825356156804</v>
       </c>
       <c r="K8" t="n">
-        <v>11.2880370047684</v>
+        <v>17.58264636752817</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72684238675173</v>
+        <v>42.23228796580094</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81178372044509</v>
+        <v>99.88763322310099</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.94451915249213</v>
+        <v>80.51377718498986</v>
       </c>
       <c r="C9" t="n">
-        <v>42.90848193585143</v>
+        <v>38.69266574887524</v>
       </c>
       <c r="D9" t="n">
-        <v>1.946513819212037</v>
+        <v>1.805646437267064</v>
       </c>
       <c r="E9" t="n">
-        <v>10.18405048260859</v>
+        <v>8.533345934916371</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508971139594287</v>
+        <v>0.7456404342461821</v>
       </c>
       <c r="G9" t="n">
-        <v>30.10473198919006</v>
+        <v>27.65314719021081</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54126724213372</v>
+        <v>34.29945997532437</v>
       </c>
       <c r="I9" t="n">
-        <v>4.723951543141887</v>
+        <v>2.816284498986435</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69310696224643</v>
+        <v>4.660252714038638</v>
       </c>
       <c r="K9" t="n">
-        <v>13.05548084750785</v>
+        <v>19.48622281501013</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87885683429087</v>
+        <v>41.72734461486805</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84281961765015</v>
+        <v>99.90623317875342</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.92462276458697</v>
+        <v>85.55871707250139</v>
       </c>
       <c r="C10" t="n">
-        <v>41.62240139805686</v>
+        <v>42.17108102745811</v>
       </c>
       <c r="D10" t="n">
-        <v>1.856290340796495</v>
+        <v>1.807656362831096</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3691260602233</v>
+        <v>10.49950175339717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520591545785595</v>
+        <v>0.7464704316030485</v>
       </c>
       <c r="G10" t="n">
-        <v>28.70933802382284</v>
+        <v>29.16439452324649</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59472111061374</v>
+        <v>35.81810554186671</v>
       </c>
       <c r="I10" t="n">
-        <v>3.942718358436034</v>
+        <v>2.857148262037835</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700369716115998</v>
+        <v>4.665440197519053</v>
       </c>
       <c r="K10" t="n">
-        <v>15.07537723541303</v>
+        <v>14.4412829274986</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17100049033172</v>
+        <v>43.29250366468288</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86877912380162</v>
+        <v>99.9048676196396</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.74562256035772</v>
+        <v>85.22144746618444</v>
       </c>
       <c r="C11" t="n">
-        <v>40.05541314719696</v>
+        <v>42.15955635763081</v>
       </c>
       <c r="D11" t="n">
-        <v>1.759807280911429</v>
+        <v>1.784035580181067</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37850301920077</v>
+        <v>10.82724799876706</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530558797594293</v>
+        <v>0.7471832485074953</v>
       </c>
       <c r="G11" t="n">
-        <v>27.21713353461315</v>
+        <v>28.84134838462326</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64057046893375</v>
+        <v>35.91035605477973</v>
       </c>
       <c r="I11" t="n">
-        <v>3.289953128442761</v>
+        <v>2.441380896153992</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706599248496434</v>
+        <v>4.669895303171845</v>
       </c>
       <c r="K11" t="n">
-        <v>17.25437743964226</v>
+        <v>14.77855253381555</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58068945875977</v>
+        <v>42.98058938170595</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89048004559899</v>
+        <v>99.91869827315232</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.37187759913807</v>
+        <v>83.22094016924072</v>
       </c>
       <c r="C12" t="n">
-        <v>38.19169268777104</v>
+        <v>40.53838859515655</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65554600324992</v>
+        <v>1.699322647594426</v>
       </c>
       <c r="E12" t="n">
-        <v>10.22107788070031</v>
+        <v>10.65248546663221</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539131236507222</v>
+        <v>0.7477926192484026</v>
       </c>
       <c r="G12" t="n">
-        <v>25.60463133202368</v>
+        <v>27.47184923978757</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68000368793322</v>
+        <v>35.93964300723624</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744748548763202</v>
+        <v>2.036143318439342</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711957022817014</v>
+        <v>4.673703870302516</v>
       </c>
       <c r="K12" t="n">
-        <v>19.62812240086195</v>
+        <v>16.77905983075928</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08879732446582</v>
+        <v>42.6147354380799</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90861241309881</v>
+        <v>99.93218386399573</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.90328905114359</v>
+        <v>84.41496136209977</v>
       </c>
       <c r="C13" t="n">
-        <v>36.14779486784728</v>
+        <v>41.53427511138752</v>
       </c>
       <c r="D13" t="n">
-        <v>1.54802354764913</v>
+        <v>1.700585049746345</v>
       </c>
       <c r="E13" t="n">
-        <v>9.938839862486923</v>
+        <v>11.29894587368507</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546516922166188</v>
+        <v>0.7483481435410166</v>
       </c>
       <c r="G13" t="n">
-        <v>23.94169183643269</v>
+        <v>27.8172512550799</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71397784196446</v>
+        <v>36.29133562372144</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289531194039891</v>
+        <v>1.881319519194658</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716573076353868</v>
+        <v>4.677175897131354</v>
       </c>
       <c r="K13" t="n">
-        <v>22.09671094885641</v>
+        <v>15.58503863790022</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6792511680529</v>
+        <v>42.81802215232238</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92375698475659</v>
+        <v>99.93733590161014</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.21911251257957</v>
+        <v>82.31171416790662</v>
       </c>
       <c r="C14" t="n">
-        <v>40.03875233219462</v>
+        <v>39.7231775055251</v>
       </c>
       <c r="D14" t="n">
-        <v>1.549845745757997</v>
+        <v>1.613980334798933</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12841935693482</v>
+        <v>10.98499134387115</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555400022739811</v>
+        <v>0.7488235640546803</v>
       </c>
       <c r="G14" t="n">
-        <v>25.65207734930634</v>
+        <v>26.40061812877665</v>
       </c>
       <c r="H14" t="n">
-        <v>36.43704354902331</v>
+        <v>36.31439126376369</v>
       </c>
       <c r="I14" t="n">
-        <v>2.974061495070749</v>
+        <v>1.568762257299753</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722125014212382</v>
+        <v>4.680147275341752</v>
       </c>
       <c r="K14" t="n">
-        <v>15.78088748742042</v>
+        <v>17.68828583209338</v>
       </c>
       <c r="L14" t="n">
-        <v>44.08134135353015</v>
+        <v>42.53627778684834</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90098117314518</v>
+        <v>99.94774112446683</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.2830946163966</v>
+        <v>81.34089331560807</v>
       </c>
       <c r="C15" t="n">
-        <v>39.56292865462774</v>
+        <v>38.96643688708152</v>
       </c>
       <c r="D15" t="n">
-        <v>1.514463435680732</v>
+        <v>1.573268706760539</v>
       </c>
       <c r="E15" t="n">
-        <v>12.26500701590442</v>
+        <v>10.93059118703299</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562902057384239</v>
+        <v>0.7492335791505208</v>
       </c>
       <c r="G15" t="n">
-        <v>25.06645148467859</v>
+        <v>25.73467931770908</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47322323007562</v>
+        <v>36.33427505125267</v>
       </c>
       <c r="I15" t="n">
-        <v>2.480845458453674</v>
+        <v>1.336135604011521</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726813785865149</v>
+        <v>4.682709869690755</v>
       </c>
       <c r="K15" t="n">
-        <v>16.71690538360341</v>
+        <v>18.65910668439192</v>
       </c>
       <c r="L15" t="n">
-        <v>43.63755314246132</v>
+        <v>42.32994294822264</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91738718069246</v>
+        <v>99.95548651969608</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.60708599406878</v>
+        <v>78.87180765690441</v>
       </c>
       <c r="C16" t="n">
-        <v>37.27076538890406</v>
+        <v>36.70426152139549</v>
       </c>
       <c r="D16" t="n">
-        <v>1.411342019455864</v>
+        <v>1.472374651121615</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77472641636053</v>
+        <v>10.41527181403261</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569373243785807</v>
+        <v>0.7495863136106985</v>
       </c>
       <c r="G16" t="n">
-        <v>23.35965030616738</v>
+        <v>24.08430887827085</v>
       </c>
       <c r="H16" t="n">
-        <v>36.5044314917187</v>
+        <v>36.35138099958814</v>
       </c>
       <c r="I16" t="n">
-        <v>2.069140158621599</v>
+        <v>1.113970540213634</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73085827736613</v>
+        <v>4.684914460066866</v>
       </c>
       <c r="K16" t="n">
-        <v>19.3929140059312</v>
+        <v>21.12819234309561</v>
       </c>
       <c r="L16" t="n">
-        <v>43.26740823131883</v>
+        <v>42.13043125761969</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9310876261541</v>
+        <v>99.96288512211078</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.03520492700549</v>
+        <v>83.80379396377501</v>
       </c>
       <c r="C17" t="n">
-        <v>38.32386305502666</v>
+        <v>39.9728687614022</v>
       </c>
       <c r="D17" t="n">
-        <v>1.412529466037132</v>
+        <v>1.473095633005005</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46821912431312</v>
+        <v>12.14942259068317</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757574181090616</v>
+        <v>0.7499533656729835</v>
       </c>
       <c r="G17" t="n">
-        <v>23.71778444519819</v>
+        <v>25.61997080038498</v>
       </c>
       <c r="H17" t="n">
-        <v>36.87362512254181</v>
+        <v>37.89304977379999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.070633956008291</v>
+        <v>1.231093264772729</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73483863181635</v>
+        <v>4.687208535456147</v>
       </c>
       <c r="K17" t="n">
-        <v>17.96479507299449</v>
+        <v>16.19620603622499</v>
       </c>
       <c r="L17" t="n">
-        <v>43.64237876290649</v>
+        <v>43.78990884481021</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93103689092764</v>
+        <v>99.9589836424374</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.46054212018711</v>
+        <v>85.43463398016165</v>
       </c>
       <c r="C18" t="n">
-        <v>36.06903245926627</v>
+        <v>40.70575113315811</v>
       </c>
       <c r="D18" t="n">
-        <v>1.31675576686768</v>
+        <v>1.474291680122808</v>
       </c>
       <c r="E18" t="n">
-        <v>11.910633153902</v>
+        <v>12.75082354892714</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581229493079323</v>
+        <v>0.7505622735683048</v>
       </c>
       <c r="G18" t="n">
-        <v>22.10964811456775</v>
+        <v>25.76312375656699</v>
       </c>
       <c r="H18" t="n">
-        <v>36.90033547517731</v>
+        <v>37.92381618974155</v>
       </c>
       <c r="I18" t="n">
-        <v>1.72677822718986</v>
+        <v>2.081002321432949</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738268433174577</v>
+        <v>4.691014209801905</v>
       </c>
       <c r="K18" t="n">
-        <v>20.53945787981288</v>
+        <v>14.56536601983836</v>
       </c>
       <c r="L18" t="n">
-        <v>43.33399205103174</v>
+        <v>44.65957237804393</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94248239011088</v>
+        <v>99.9306895310404</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.37964771528843</v>
+        <v>82.70177234828094</v>
       </c>
       <c r="C19" t="n">
-        <v>35.2540958890786</v>
+        <v>38.29496772750354</v>
       </c>
       <c r="D19" t="n">
-        <v>1.277260296938065</v>
+        <v>1.374496901102467</v>
       </c>
       <c r="E19" t="n">
-        <v>11.79335648263929</v>
+        <v>12.1769507793962</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585871825724463</v>
+        <v>0.7510872570525171</v>
       </c>
       <c r="G19" t="n">
-        <v>21.44647961799792</v>
+        <v>24.01921834298822</v>
       </c>
       <c r="H19" t="n">
-        <v>36.92293123384012</v>
+        <v>37.9503421394982</v>
       </c>
       <c r="I19" t="n">
-        <v>1.439863010222791</v>
+        <v>1.735381571665099</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741169891077789</v>
+        <v>4.694295356578231</v>
       </c>
       <c r="K19" t="n">
-        <v>21.62035228471157</v>
+        <v>17.29822765171908</v>
       </c>
       <c r="L19" t="n">
-        <v>43.07758576434344</v>
+        <v>44.34899900073758</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95203393813361</v>
+        <v>99.94219437996018</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.75292282771383</v>
+        <v>79.89689952229368</v>
       </c>
       <c r="C20" t="n">
-        <v>32.84893966621518</v>
+        <v>35.757905672839</v>
       </c>
       <c r="D20" t="n">
-        <v>1.180685136658281</v>
+        <v>1.272650405164204</v>
       </c>
       <c r="E20" t="n">
-        <v>11.1017334796084</v>
+        <v>11.51584244854347</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589879146801843</v>
+        <v>0.7515406920679935</v>
       </c>
       <c r="G20" t="n">
-        <v>19.82488595262645</v>
+        <v>22.23945934793537</v>
       </c>
       <c r="H20" t="n">
-        <v>36.94243618250934</v>
+        <v>37.97325294488569</v>
       </c>
       <c r="I20" t="n">
-        <v>1.200519694880029</v>
+        <v>1.447024358271996</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743674466751151</v>
+        <v>4.697129325424958</v>
       </c>
       <c r="K20" t="n">
-        <v>24.24707717228617</v>
+        <v>20.1031004777063</v>
       </c>
       <c r="L20" t="n">
-        <v>42.86398696677024</v>
+        <v>44.09078880579735</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96000380527158</v>
+        <v>99.95179495634267</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.67211535606688</v>
+        <v>77.08745175200468</v>
       </c>
       <c r="C21" t="n">
-        <v>36.52004209593642</v>
+        <v>33.17102072873758</v>
       </c>
       <c r="D21" t="n">
-        <v>1.181517137144264</v>
+        <v>1.171187041167349</v>
       </c>
       <c r="E21" t="n">
-        <v>13.08159971588184</v>
+        <v>10.79881050465748</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759522755252207</v>
+        <v>0.75193276662616</v>
       </c>
       <c r="G21" t="n">
-        <v>21.52313728504696</v>
+        <v>20.46639555150205</v>
       </c>
       <c r="H21" t="n">
-        <v>38.65274984185166</v>
+        <v>37.99306337767749</v>
       </c>
       <c r="I21" t="n">
-        <v>1.726571400563642</v>
+        <v>1.206482718960642</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747017220326293</v>
+        <v>4.6995797914135</v>
       </c>
       <c r="K21" t="n">
-        <v>18.32788464393314</v>
+        <v>22.91254824799531</v>
       </c>
       <c r="L21" t="n">
-        <v>45.09456140733436</v>
+        <v>43.87623590220399</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94248814720392</v>
+        <v>99.95980487893689</v>
       </c>
     </row>
   </sheetData>
